--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Dead hang (agarre)</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t xml:space="preserve">Notas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serie máx. 29 s, objetivo 31 s (no alcanzado). Respaldo 15 + 10 s (la 3ª se quedó en 10, por debajo de los 15 pautados). Total 54 s. Récord vigente: 30 s.</t>
   </si>
   <si>
     <t xml:space="preserve">Récord serie máxima (s)</t>
@@ -247,7 +250,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -293,38 +296,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1299,16 +1270,16 @@
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1323,51 +1294,51 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -1379,533 +1350,539 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="10" t="n">
         <v>46279</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="9" t="n">
         <f aca="false">IF($B$6="","",$B$6)</f>
         <v>31</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="17" t="str">
+      <c r="D12" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <f aca="false">IF(D12="","",D12+IF(E12="",0,E12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">IF(B12="","",B12+IF(WEEKDAY(B12,2)=1,4,3))</f>
         <v>46283</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">IF(C12="","",C12+IF($B$7="",0,$B$7))</f>
         <v>32</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="17" t="str">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="9" t="str">
         <f aca="false">IF(D13="","",D13+IF(E13="",0,E13))</f>
         <v/>
       </c>
-      <c r="G13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="11" t="n">
         <f aca="false">IF(B13="","",B13+IF(WEEKDAY(B13,2)=1,4,3))</f>
         <v>46286</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="9" t="n">
         <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
         <v>33</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="17" t="str">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="9" t="str">
         <f aca="false">IF(D14="","",D14+IF(E14="",0,E14))</f>
         <v/>
       </c>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="11" t="n">
         <f aca="false">IF(B14="","",B14+IF(WEEKDAY(B14,2)=1,4,3))</f>
         <v>46290</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="9" t="n">
         <f aca="false">IF(C14="","",C14+IF($B$7="",0,$B$7))</f>
         <v>34</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="17" t="str">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="9" t="str">
         <f aca="false">IF(D15="","",D15+IF(E15="",0,E15))</f>
         <v/>
       </c>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="11" t="n">
         <f aca="false">IF(B15="","",B15+IF(WEEKDAY(B15,2)=1,4,3))</f>
         <v>46293</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="9" t="n">
         <f aca="false">IF(C15="","",C15+IF($B$7="",0,$B$7))</f>
         <v>35</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="17" t="str">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="9" t="str">
         <f aca="false">IF(D16="","",D16+IF(E16="",0,E16))</f>
         <v/>
       </c>
-      <c r="G16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="11" t="n">
         <f aca="false">IF(B16="","",B16+IF(WEEKDAY(B16,2)=1,4,3))</f>
         <v>46297</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="9" t="n">
         <f aca="false">IF(C16="","",C16+IF($B$7="",0,$B$7))</f>
         <v>36</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="17" t="str">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="9" t="str">
         <f aca="false">IF(D17="","",D17+IF(E17="",0,E17))</f>
         <v/>
       </c>
-      <c r="G17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="11" t="n">
         <f aca="false">IF(B17="","",B17+IF(WEEKDAY(B17,2)=1,4,3))</f>
         <v>46300</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="9" t="n">
         <f aca="false">IF(C17="","",C17+IF($B$7="",0,$B$7))</f>
         <v>37</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="str">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="9" t="str">
         <f aca="false">IF(D18="","",D18+IF(E18="",0,E18))</f>
         <v/>
       </c>
-      <c r="G18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="11" t="n">
         <f aca="false">IF(B18="","",B18+IF(WEEKDAY(B18,2)=1,4,3))</f>
         <v>46304</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="9" t="n">
         <f aca="false">IF(C18="","",C18+IF($B$7="",0,$B$7))</f>
         <v>38</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="17" t="str">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="9" t="str">
         <f aca="false">IF(D19="","",D19+IF(E19="",0,E19))</f>
         <v/>
       </c>
-      <c r="G19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="11" t="n">
         <f aca="false">IF(B19="","",B19+IF(WEEKDAY(B19,2)=1,4,3))</f>
         <v>46307</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="9" t="n">
         <f aca="false">IF(C19="","",C19+IF($B$7="",0,$B$7))</f>
         <v>39</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="17" t="str">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="9" t="str">
         <f aca="false">IF(D20="","",D20+IF(E20="",0,E20))</f>
         <v/>
       </c>
-      <c r="G20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="n">
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="11" t="n">
         <f aca="false">IF(B20="","",B20+IF(WEEKDAY(B20,2)=1,4,3))</f>
         <v>46311</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="9" t="n">
         <f aca="false">IF(C20="","",C20+IF($B$7="",0,$B$7))</f>
         <v>40</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="17" t="str">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="9" t="str">
         <f aca="false">IF(D21="","",D21+IF(E21="",0,E21))</f>
         <v/>
       </c>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="n">
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="11" t="n">
         <f aca="false">IF(B21="","",B21+IF(WEEKDAY(B21,2)=1,4,3))</f>
         <v>46314</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="9" t="n">
         <f aca="false">IF(C21="","",C21+IF($B$7="",0,$B$7))</f>
         <v>41</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="17" t="str">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="9" t="str">
         <f aca="false">IF(D22="","",D22+IF(E22="",0,E22))</f>
         <v/>
       </c>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="n">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="11" t="n">
         <f aca="false">IF(B22="","",B22+IF(WEEKDAY(B22,2)=1,4,3))</f>
         <v>46318</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="9" t="n">
         <f aca="false">IF(C22="","",C22+IF($B$7="",0,$B$7))</f>
         <v>42</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="17" t="str">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="9" t="str">
         <f aca="false">IF(D23="","",D23+IF(E23="",0,E23))</f>
         <v/>
       </c>
-      <c r="G23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="n">
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="11" t="n">
         <f aca="false">IF(B23="","",B23+IF(WEEKDAY(B23,2)=1,4,3))</f>
         <v>46321</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="9" t="n">
         <f aca="false">IF(C23="","",C23+IF($B$7="",0,$B$7))</f>
         <v>43</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="17" t="str">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="9" t="str">
         <f aca="false">IF(D24="","",D24+IF(E24="",0,E24))</f>
         <v/>
       </c>
-      <c r="G24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="n">
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="11" t="n">
         <f aca="false">IF(B24="","",B24+IF(WEEKDAY(B24,2)=1,4,3))</f>
         <v>46325</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="9" t="n">
         <f aca="false">IF(C24="","",C24+IF($B$7="",0,$B$7))</f>
         <v>44</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="17" t="str">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="9" t="str">
         <f aca="false">IF(D25="","",D25+IF(E25="",0,E25))</f>
         <v/>
       </c>
-      <c r="G25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="n">
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="11" t="n">
         <f aca="false">IF(B25="","",B25+IF(WEEKDAY(B25,2)=1,4,3))</f>
         <v>46328</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="9" t="n">
         <f aca="false">IF(C25="","",C25+IF($B$7="",0,$B$7))</f>
         <v>45</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="17" t="str">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="9" t="str">
         <f aca="false">IF(D26="","",D26+IF(E26="",0,E26))</f>
         <v/>
       </c>
-      <c r="G26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="n">
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="11" t="n">
         <f aca="false">IF(B26="","",B26+IF(WEEKDAY(B26,2)=1,4,3))</f>
         <v>46332</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="9" t="n">
         <f aca="false">IF(C26="","",C26+IF($B$7="",0,$B$7))</f>
         <v>46</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="17" t="str">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="9" t="str">
         <f aca="false">IF(D27="","",D27+IF(E27="",0,E27))</f>
         <v/>
       </c>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="n">
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="11" t="n">
         <f aca="false">IF(B27="","",B27+IF(WEEKDAY(B27,2)=1,4,3))</f>
         <v>46335</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="9" t="n">
         <f aca="false">IF(C27="","",C27+IF($B$7="",0,$B$7))</f>
         <v>47</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="17" t="str">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="9" t="str">
         <f aca="false">IF(D28="","",D28+IF(E28="",0,E28))</f>
         <v/>
       </c>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="n">
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="11" t="n">
         <f aca="false">IF(B28="","",B28+IF(WEEKDAY(B28,2)=1,4,3))</f>
         <v>46339</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="9" t="n">
         <f aca="false">IF(C28="","",C28+IF($B$7="",0,$B$7))</f>
         <v>48</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="17" t="str">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="9" t="str">
         <f aca="false">IF(D29="","",D29+IF(E29="",0,E29))</f>
         <v/>
       </c>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="n">
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="11" t="n">
         <f aca="false">IF(B29="","",B29+IF(WEEKDAY(B29,2)=1,4,3))</f>
         <v>46342</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="9" t="n">
         <f aca="false">IF(C29="","",C29+IF($B$7="",0,$B$7))</f>
         <v>49</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="17" t="str">
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="9" t="str">
         <f aca="false">IF(D30="","",D30+IF(E30="",0,E30))</f>
         <v/>
       </c>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="n">
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="11" t="n">
         <f aca="false">IF(B30="","",B30+IF(WEEKDAY(B30,2)=1,4,3))</f>
         <v>46346</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="9" t="n">
         <f aca="false">IF(C30="","",C30+IF($B$7="",0,$B$7))</f>
         <v>50</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="17" t="str">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="9" t="str">
         <f aca="false">IF(D31="","",D31+IF(E31="",0,E31))</f>
         <v/>
       </c>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="n">
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B32" s="11" t="n">
         <f aca="false">IF(B31="","",B31+IF(WEEKDAY(B31,2)=1,4,3))</f>
         <v>46349</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="9" t="n">
         <f aca="false">IF(C31="","",C31+IF($B$7="",0,$B$7))</f>
         <v>51</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="17" t="str">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="9" t="str">
         <f aca="false">IF(D32="","",D32+IF(E32="",0,E32))</f>
         <v/>
       </c>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="n">
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="11" t="n">
         <f aca="false">IF(B32="","",B32+IF(WEEKDAY(B32,2)=1,4,3))</f>
         <v>46353</v>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C33" s="9" t="n">
         <f aca="false">IF(C32="","",C32+IF($B$7="",0,$B$7))</f>
         <v>52</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="17" t="str">
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="9" t="str">
         <f aca="false">IF(D33="","",D33+IF(E33="",0,E33))</f>
         <v/>
       </c>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="n">
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="19" t="n">
+      <c r="B34" s="11" t="n">
         <f aca="false">IF(B33="","",B33+IF(WEEKDAY(B33,2)=1,4,3))</f>
         <v>46356</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="9" t="n">
         <f aca="false">IF(C33="","",C33+IF($B$7="",0,$B$7))</f>
         <v>53</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="17" t="str">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="9" t="str">
         <f aca="false">IF(D34="","",D34+IF(E34="",0,E34))</f>
         <v/>
       </c>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="n">
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="11" t="n">
         <f aca="false">IF(B34="","",B34+IF(WEEKDAY(B34,2)=1,4,3))</f>
         <v>46360</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C35" s="9" t="n">
         <f aca="false">IF(C34="","",C34+IF($B$7="",0,$B$7))</f>
         <v>54</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="17" t="str">
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="9" t="str">
         <f aca="false">IF(D35="","",D35+IF(E35="",0,E35))</f>
         <v/>
       </c>
-      <c r="G35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="17" t="n">
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="9" t="n">
         <f aca="false">MAX(D12:D35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="17" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <f aca="false">MAX(F12:F35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <f aca="false">SUM(F12:F35)</f>
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -701,64 +701,134 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
+      <c r="A16" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Prensa</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="E16" s="17" t="n"/>
       <c r="F16" s="18">
         <f>IF(D16="","",IF(D16&gt;=120,"Subir carga",IF(D16&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G16" s="17" t="n"/>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Primera sesión con prensa dinámica (Slow Fit 10/10). Dentro del rango objetivo: mantener carga.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
+      <c r="A17" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Jalón al pecho divergente</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>75</v>
+      </c>
       <c r="E17" s="17" t="n"/>
       <c r="F17" s="18">
         <f>IF(D17="","",IF(D17&gt;=120,"Subir carga",IF(D17&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G17" s="17" t="n"/>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 18 a 23 kg y el tiempo baja de 120 a 75 s. Mantener 23 kg y buscar más tiempo.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
+      <c r="A18" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Chest press</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="E18" s="17" t="n"/>
       <c r="F18" s="18">
         <f>IF(D18="","",IF(D18&gt;=120,"Subir carga",IF(D18&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G18" s="17" t="n"/>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Repite 18 kg y 60 s, igual que el 16/09. Mantener carga y buscar más tiempo.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
+      <c r="A19" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Remo sentado en máquina</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>45</v>
+      </c>
       <c r="E19" s="17" t="n"/>
       <c r="F19" s="18">
         <f>IF(D19="","",IF(D19&gt;=120,"Subir carga",IF(D19&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G19" s="17" t="n"/>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 18 a 23 kg (+5) y el tiempo cae de 120 a 45 s. Valorar bajar a ~20 kg.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
+      <c r="A20" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Press hombro convergente</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="E20" s="17" t="n"/>
       <c r="F20" s="18">
         <f>IF(D20="","",IF(D20&gt;=120,"Subir carga",IF(D20&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Repite 14 kg y 60 s, igual que el 16/09. Mantener carga y buscar más tiempo.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n"/>

--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -535,6 +535,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Placa mínima: si la carga más baja de una máquina deja el TUT por debajo de 90 s, se mantiene y se suman segundos. No se cambia de máquina ni se acorta el recorrido. Caso: press hombro, 14 kg.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
@@ -788,7 +795,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19" s="17" t="n">
         <v>45</v>
@@ -800,7 +807,7 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>Sube de 18 a 23 kg (+5) y el tiempo cae de 120 a 45 s. Valorar bajar a ~20 kg.</t>
+          <t>Sube de 18 a 25 kg (+7) y el tiempo cae de 120 a 45 s. Carga corregida: eran 25 kg, no 23.</t>
         </is>
       </c>
     </row>
@@ -831,184 +838,394 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
+      <c r="A21" s="16" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Prensa</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>120</v>
+      </c>
       <c r="E21" s="17" t="n"/>
       <c r="F21" s="18">
         <f>IF(D21="","",IF(D21&gt;=120,"Subir carga",IF(D21&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G21" s="17" t="n"/>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>120 s: toca subir una placa la próxima sesión.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
+      <c r="A22" s="16" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Jalón al pecho divergente</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>90</v>
+      </c>
       <c r="E22" s="17" t="n"/>
       <c r="F22" s="18">
         <f>IF(D22="","",IF(D22&gt;=120,"Subir carga",IF(D22&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G22" s="17" t="n"/>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 75 a 90 s con los mismos 23 kg. Ya en rango: mantener.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
+      <c r="A23" s="16" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Chest press</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="E23" s="17" t="n"/>
       <c r="F23" s="18">
         <f>IF(D23="","",IF(D23&gt;=120,"Subir carga",IF(D23&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G23" s="17" t="n"/>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Tercera sesión seguida en 60 s con 18 kg. Valorar bajar un escalón para poder llegar a 90 s.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
+      <c r="A24" s="16" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Remo sentado en máquina</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>45</v>
+      </c>
       <c r="E24" s="17" t="n"/>
       <c r="F24" s="18">
         <f>IF(D24="","",IF(D24&gt;=120,"Subir carga",IF(D24&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G24" s="17" t="n"/>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Segunda sesión en 45 s con 25 kg. Valorar bajar a ~20 kg.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
+      <c r="A25" s="16" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Press hombro convergente</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18">
         <f>IF(D25="","",IF(D25&gt;=120,"Subir carga",IF(D25&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G25" s="17" t="n"/>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Tercera sesión seguida en 60 s con 14 kg. Valorar bajar un escalón.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
+      <c r="A26" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Prensa</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>120</v>
+      </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18">
         <f>IF(D26="","",IF(D26&gt;=120,"Subir carga",IF(D26&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G26" s="17" t="n"/>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Segunda sesión seguida en 120 s. Pendiente subir una placa (ya tocaba el 08/10).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
+      <c r="A27" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Jalón al pecho divergente</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>90</v>
+      </c>
       <c r="E27" s="17" t="n"/>
       <c r="F27" s="18">
         <f>IF(D27="","",IF(D27&gt;=120,"Subir carga",IF(D27&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G27" s="17" t="n"/>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Repite los 90 s del martes. Segunda sesión de la semana sin caída.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
+      <c r="A28" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Chest press</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="E28" s="17" t="n"/>
       <c r="F28" s="18">
         <f>IF(D28="","",IF(D28&gt;=120,"Subir carga",IF(D28&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G28" s="17" t="n"/>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 60 a 65 s. Primera mejora tras tres sesiones clavadas.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
+      <c r="A29" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Remo sentado en máquina</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="E29" s="17" t="n"/>
       <c r="F29" s="18">
         <f>IF(D29="","",IF(D29&gt;=120,"Subir carga",IF(D29&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G29" s="17" t="n"/>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 45 a 65 s con los mismos 25 kg. Mejor salto de la semana.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
+      <c r="A30" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Press hombro convergente</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="E30" s="17" t="n"/>
       <c r="F30" s="18">
         <f>IF(D30="","",IF(D30&gt;=120,"Subir carga",IF(D30&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G30" s="17" t="n"/>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Cuarta sesión seguida en 60 s. Es la única máquina que no se mueve: valorar bajar un escalón.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
+      <c r="A31" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Prensa</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>70</v>
+      </c>
       <c r="E31" s="17" t="n"/>
       <c r="F31" s="18">
         <f>IF(D31="","",IF(D31&gt;=120,"Subir carga",IF(D31&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G31" s="17" t="n"/>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>**Rango acortado** desde hoy: el usuario quita el tramo en el que la palanca aliviaba el esfuerzo. Por eso baja de 120 a 70 s. No comparable con las sesiones anteriores: 70 s es la nueva referencia.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="n"/>
+      <c r="A32" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Jalón al pecho divergente</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>90</v>
+      </c>
       <c r="E32" s="17" t="n"/>
       <c r="F32" s="18">
         <f>IF(D32="","",IF(D32&gt;=120,"Subir carga",IF(D32&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G32" s="17" t="n"/>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Tercera sesión en 90 s con 23 kg. En rango, estable.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
+      <c r="A33" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Chest press</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>70</v>
+      </c>
       <c r="E33" s="17" t="n"/>
       <c r="F33" s="18">
         <f>IF(D33="","",IF(D33&gt;=120,"Subir carga",IF(D33&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G33" s="17" t="n"/>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 65 a 70 s. Tercera mejora seguida (60 → 65 → 70).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="17" t="n"/>
+      <c r="A34" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Remo sentado en máquina</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>80</v>
+      </c>
       <c r="E34" s="17" t="n"/>
       <c r="F34" s="18">
         <f>IF(D34="","",IF(D34&gt;=120,"Subir carga",IF(D34&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G34" s="17" t="n"/>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Sube de 65 a 80 s. Acercándose al rango (45 → 65 → 80).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
+      <c r="A35" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Press hombro convergente</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>68</v>
+      </c>
       <c r="E35" s="17" t="n"/>
       <c r="F35" s="18">
         <f>IF(D35="","",IF(D35&gt;=120,"Subir carga",IF(D35&gt;=90,"Mantener","Mantener y subir tiempo")))</f>
         <v/>
       </c>
-      <c r="G35" s="17" t="n"/>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>**Primer avance**: de 60 a 68 s tras cuatro sesiones clavadas. Carga mínima de la máquina, se progresa solo en tiempo.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n"/>
